--- a/Operacional/Modelos/CRONOGRAMA_CLIENTE.xlsx
+++ b/Operacional/Modelos/CRONOGRAMA_CLIENTE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr codeName="EstaPasta_de_trabalho" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CIPOLATTI\SISTEMAS\Operacional\Operacional\Modelos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\Codex\2026-05-21\clona-o-repositorio-wognascimento-financeiro-git\Operacional\Operacional\Modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C9EF41-9302-4C4B-94E7-6DD43A88AA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831525AF-E3FF-4FD1-A617-3FC14C5982C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,6 @@
     <sheet name="Plan2" sheetId="2" r:id="rId2"/>
     <sheet name="Plan3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">CLIENTE!$A$1:$U$12</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -294,6 +291,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -308,9 +308,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -723,27 +720,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
+      <c r="A1" s="14"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
       <c r="V1" s="11" t="s">
         <v>20</v>
       </c>
@@ -752,62 +749,62 @@
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
       <c r="V2" s="9"/>
       <c r="W2" s="9"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="16"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
       <c r="V3" s="9"/>
       <c r="W3" s="9"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="17" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="17"/>
+      <c r="D4" s="18"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
@@ -824,13 +821,13 @@
       <c r="R4" s="10"/>
       <c r="S4" s="10"/>
       <c r="T4" s="10"/>
-      <c r="U4" s="13"/>
+      <c r="U4" s="14"/>
       <c r="V4" s="9"/>
       <c r="W4" s="9"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
       <c r="C5" s="3"/>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
@@ -848,7 +845,7 @@
       <c r="R5" s="12"/>
       <c r="S5" s="12"/>
       <c r="T5" s="12"/>
-      <c r="U5" s="14"/>
+      <c r="U5" s="15"/>
       <c r="V5" s="9"/>
       <c r="W5" s="9"/>
     </row>
@@ -945,8 +942,8 @@
       <c r="W7" s="9"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
@@ -967,8 +964,8 @@
       <c r="W8" s="9"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
@@ -989,8 +986,8 @@
       <c r="W9" s="9"/>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
@@ -1011,8 +1008,8 @@
       <c r="W10" s="9"/>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
@@ -1033,8 +1030,8 @@
       <c r="W11" s="9"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
@@ -1237,7 +1234,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="72" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
